--- a/Test Case 배민.xlsx
+++ b/Test Case 배민.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vudck\OneDrive\문서\QA\배민\baemin-automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{396A83B1-E665-4102-B8EE-5FD16BEF64C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5E23947-E7D6-45B5-A9AA-2A41DC716AD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="147">
   <si>
     <t>TC_ID</t>
   </si>
@@ -494,55 +494,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>찜 등록</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>가게 상세 화면에서 찜(하트) 등록 및 활성화 확인</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>무작위로 매장 페이지 클릭</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">매장 하트 버튼을 누름
-이후 찜 목록에서 확인 </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>찜 목록에 해당 매장이 노출되면 성공</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>HT_02</t>
-  </si>
-  <si>
-    <t>찜 해제</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>가게 상세 화면에서 찜(하트) 해제 
-및 비활성화 확인</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>찜 목록에서 찜한 매장 페이지로 이동</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>매장 페이지의 색이 칠해져 있는 하트를 재클릭</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>찜 목록에서 삭제되어야 함(찜 취소)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>HT_03</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>찜 목록</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -568,23 +519,104 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>HT_04</t>
-  </si>
-  <si>
-    <t>비로그인 상태에서 찜(하트) 클릭 시 로그인 유도 분기 검증</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>로그인을 하지 않은 상태</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>가게 찜 눌러보기</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>로그인이 필요하단 토스트 메시지가 표시되고,
-로그인 창으로 전환</t>
+    <t>ADDR_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>주소</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>주소추가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Negative (Exception)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">주소 검색' 화면으로 진입한 상태 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>앱이 멈추거나 Crash가 발생하지 않고, "검색 결과가 없습니다" 안내 메시지와 함께 재검색을 유도해야 함.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ADDR_02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">잘못된 주소 형식 처리 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">새로운 주소 추가 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ADDR_03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">주소 삭제 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>등록된 주소 삭제</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>등록한 주소 목록</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ADDR_04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">주소 설정' 화면으로 진입한 상태 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.검색창 누르고 주소 검색 화면으로 이동
+2.'주소 검색창에 '%%' 처럼 특수문자 입력</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>새로운 주소 등록 완료 (주소 설정 화면에서 확인가능)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">필수 데이터 입력 안했을 경우 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 주소 검색창에 특정 주소 입력 (예시로 연세대 과학관)
+2. 결과에 '연세대학교 과학관'이라 나와있는 부분 클릭
+3. 상세 설정 화면에서 상세 주소 입력 안하고 다른 입력창(ex. 공동현관 비밀번호) 클릭</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">정확한 상세주소를 입력해주세요'  라는 빨간 멘트가 노출되어야 한다 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 주소 상세 화면으로 진입했다면 상세주소에 '1F'라고 작성
+2. 주소등록 버튼 클릭</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>기존에 있는 주소에 '삭제'버튼 클릭</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>삭제한 주소가 더 이상 주소 목록에 안 나오면 됌</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>기능 검증</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>데이터 연동</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -656,7 +688,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -678,9 +710,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -962,7 +991,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr defaultRowHeight="16.899999999999999"/>
   <cols>
     <col min="1" max="3" width="9" style="4"/>
@@ -975,7 +1004,7 @@
     <col min="10" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="27.75">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1468,7 +1497,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="33.75">
+    <row r="18" spans="1:9" ht="50.65">
       <c r="A18" s="4" t="s">
         <v>114</v>
       </c>
@@ -1478,110 +1507,139 @@
       <c r="C18" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="4" t="s">
         <v>117</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>66</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="G18" s="4" t="s">
         <v>118</v>
       </c>
+      <c r="G18" s="5" t="s">
+        <v>119</v>
+      </c>
       <c r="H18" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="50.65">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="67.5">
       <c r="A19" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>74</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="G19" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="118.15">
+      <c r="A20" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="D20" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="I19" s="4" t="s">
+      <c r="G20" s="6" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" ht="50.65">
-      <c r="A20" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>133</v>
+      <c r="H20" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="50.65">
       <c r="A21" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G22" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="I21" s="5" t="s">
-        <v>138</v>
+      <c r="H22" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>
